--- a/example/data/default_session/example_data/inventory.xlsx
+++ b/example/data/default_session/example_data/inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wsg\PycharmProjects\Algomancy\example\data\default_session\example_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38A664A5-7549-4963-B360-495C5480437F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2893276-0F06-4245-9799-4AB9C422422F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet E1-03-04-0001      " sheetId="2" r:id="rId1"/>
@@ -34,13 +34,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
   <si>
     <t>Branch</t>
-  </si>
-  <si>
-    <t>Location 
-Type P/S</t>
   </si>
   <si>
     <t>Location</t>
@@ -247,6 +243,9 @@
   </si>
   <si>
     <t>20</t>
+  </si>
+  <si>
+    <t>LocationType \nP/S</t>
   </si>
 </sst>
 </file>
@@ -978,106 +977,104 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="P2" s="4">
         <v>72.253500000000003</v>
@@ -1097,47 +1094,45 @@
     </row>
     <row r="3" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>21</v>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>32</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="P3" s="4">
         <v>47.72</v>
@@ -1157,47 +1152,45 @@
     </row>
     <row r="4" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>21</v>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>37</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="P4" s="4">
         <v>24.574000000000002</v>
@@ -1217,45 +1210,43 @@
     </row>
     <row r="5" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>41</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="P5" s="4">
         <v>1784.4202</v>
@@ -1275,47 +1266,45 @@
     </row>
     <row r="6" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>21</v>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>44</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="P6" s="4">
         <v>23.397099999999998</v>
@@ -1335,47 +1324,45 @@
     </row>
     <row r="7" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>48</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="N7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="O7" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="P7" s="4">
         <v>11.38</v>
@@ -1395,45 +1382,43 @@
     </row>
     <row r="8" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>21</v>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="P8" s="4">
         <v>86.209699999999998</v>
@@ -1453,45 +1438,43 @@
     </row>
     <row r="9" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="P9" s="4">
         <v>86.209699999999998</v>
@@ -1511,49 +1494,47 @@
     </row>
     <row r="10" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="L10" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="P10" s="4">
         <v>5291.54</v>
